--- a/data/demo/Megaluz-Traffic-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/Megaluz-Traffic-2026-07-20~2026-07-20.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="235">
   <si>
     <t>2026-07-20</t>
   </si>
@@ -23,652 +23,700 @@
     <t>Altavoz Inalámbrico BT 5.4 Portátil - 4H Playtime/FM Radio/TWS/AUX/TF - Ideal para Fiestas y Viajes en México</t>
   </si>
   <si>
-    <t>64582</t>
-  </si>
-  <si>
-    <t>51664</t>
+    <t>95167</t>
+  </si>
+  <si>
+    <t>75505</t>
+  </si>
+  <si>
+    <t>1304</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>1.37%</t>
+  </si>
+  <si>
+    <t>602366728346713</t>
+  </si>
+  <si>
+    <t>Megaluz，Ventilador de Techo con Lámpara LED，de 13 Pulgadas， 4 Velocidades, 6 Aspas, Control Remoto, 24 vatios Regulables, Flujo Luminoso de 2200 lm, Silencioso y Eficiente,Adecuado para Dormitorios y Salas</t>
+  </si>
+  <si>
+    <t>34205</t>
+  </si>
+  <si>
+    <t>27018</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>565</t>
+  </si>
+  <si>
+    <t>1.84%</t>
+  </si>
+  <si>
+    <t>602378203945399</t>
+  </si>
+  <si>
+    <t>Dispensador de Agua para Garrafón 5L a 20L, Bomba Eléctrica Recargable USB, Flujo rápido 1500ml/min, tubo de salida acero inoxidable 304, portátil y compacto, cuerpo duradero ABS+PP, fácil instalación y operación con un solo botón, ideal para hogar, cocina, oficina y camping, práctico para uso diario en casa y exteriores.</t>
+  </si>
+  <si>
+    <t>51327</t>
+  </si>
+  <si>
+    <t>42795</t>
+  </si>
+  <si>
+    <t>752</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>1.47%</t>
+  </si>
+  <si>
+    <t>604735604161733</t>
+  </si>
+  <si>
+    <t>La bocina portátil inalámbrica Linkbits cuenta con parlantes estéreo de dos altavoces de 3 pulgadas, luces de ambiente integradas y una batería recargable de gran capacidad que ofrece 3-4 horas de reproducción. Compatible con tarjeta TF, USB, radio FM y conexión inalámbrica, es ideal para cine en casa, fiestas al aire libre y campamentos.</t>
+  </si>
+  <si>
+    <t>32230</t>
+  </si>
+  <si>
+    <t>26506</t>
+  </si>
+  <si>
+    <t>772</t>
+  </si>
+  <si>
+    <t>690</t>
+  </si>
+  <si>
+    <t>2.40%</t>
+  </si>
+  <si>
+    <t>604950620924263</t>
+  </si>
+  <si>
+    <t>Abanico portátil, ventilador evaporativo de enfriamiento con pulverización y luz nocturna, 3 velocidades ajustables, funcionamiento silencioso, alimentación USB TYPE-C, compacto con asa, abanico multifuncional para el hogar y escritorio.</t>
+  </si>
+  <si>
+    <t>12433</t>
+  </si>
+  <si>
+    <t>8973</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>2.42%</t>
+  </si>
+  <si>
+    <t>604800615833335</t>
+  </si>
+  <si>
+    <t>Cable Extensión Eléctrico Blanco SPT-2 18 AWG 2 Hilos, PVC Retardante al Fuego con Enchufe Plano Polarizado, Cable Eléctrico Seguro para Uso Interior en Casa y Oficina</t>
+  </si>
+  <si>
+    <t>8011</t>
+  </si>
+  <si>
+    <t>6293</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>1.81%</t>
+  </si>
+  <si>
+    <t>604556557710403</t>
+  </si>
+  <si>
+    <t>KBroad Altavoz BT, con 1 Micrófono Inalámbrico Gratis, Altavoz para Karaoke con Calidad HiFi, 2 Altavoces de 6W de Buena Calidad, Modo Luz RGB, Batería de Carga Integrada de 1800mAh (2-3 Horas de Duración), Compatibilidad con Tarjeta TF, Radio FM y Función TWS, Carga por TYPE-C. Ideal para Home Cinema, Karaoke y Actividades al Aire Libre.</t>
+  </si>
+  <si>
+    <t>20554</t>
+  </si>
+  <si>
+    <t>16023</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>1.89%</t>
+  </si>
+  <si>
+    <t>605011069265793</t>
+  </si>
+  <si>
+    <t>Auriculares Bluetooth 5.3 supraaurales plegables y ligeros, adecuados para todas las edades, con almohadillas transpirables, controlador de grafeno y 3 modos de conexión: Bluetooth, tarjeta TF y cableado</t>
+  </si>
+  <si>
+    <t>17635</t>
+  </si>
+  <si>
+    <t>13854</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>1.97%</t>
+  </si>
+  <si>
+    <t>604860426636252</t>
+  </si>
+  <si>
+    <t>【TIANLAI】Cabeza de farola, 100W, múltiples ledes 2835/5000lm, vida útil larga de 50000h, amplio rango de iluminación, buena impermeabilidad y disipación de calor, se instala con varios estilos de postes, voltaje de trabajo 127V, ideal para canchas de deporte, carreteras, túneles y otros escenarios.</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1501</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>2.94%</t>
+  </si>
+  <si>
+    <t>604903426610284</t>
+  </si>
+  <si>
+    <t>MEGALUZ Foco LED de 20W-60W, 1800-5700 lm Ultra brillante, luz blanca fría de 6500K, base E27, ahorro energético y alta eficiencia para hogar, tienda y garaje</t>
+  </si>
+  <si>
+    <t>2487</t>
+  </si>
+  <si>
+    <t>1952</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>4.14%</t>
+  </si>
+  <si>
+    <t>605444542175386</t>
+  </si>
+  <si>
+    <t>Linkbits Bocina Portátil BT Está Equipada Con Un Altavoz De 8 Pulgadas Y Luces De Ambiente Incorporadas. Tiene Una Duración De 2 Horas Y Viene Con Un Micrófono Cableado. Es Compatible Con La Radio FM Y La Función TWS (True Wireless Stereo), Soporta Tarjetas TF Y Se Puede Conectar A Través De USB. Cuenta Con Una Asa Y Una Pantalla De Visualización, Y También Tiene La Función De Ajuste De EQ Para El Sonido. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
+  </si>
+  <si>
+    <t>5475</t>
+  </si>
+  <si>
+    <t>4007</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>2.92%</t>
+  </si>
+  <si>
+    <t>602936750997572</t>
+  </si>
+  <si>
+    <t>¡Apto para múltiples escenarios! La lámpara LED de hojas de la marca TIANLAI, con una potencia de 36 vatios, tiene un conector E27 universal y un panel plegable de 4 hojas. El blanco brillante de 6500K es adecuado tanto para salones, dormitorios, cocinas como para garajes.</t>
+  </si>
+  <si>
+    <t>3833</t>
+  </si>
+  <si>
+    <t>3158</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>1.77%</t>
+  </si>
+  <si>
+    <t>604925924855305</t>
+  </si>
+  <si>
+    <t>MEGALUZ Tomacorrientes de Pared USB con 2 Puertos USB y 2 Tomacorrientes Estándar: Carga Rápida, Instalación Fácil, Resistencia a Altas Temperaturas y Materiales de Alta Calidad y Alto Rendimiento</t>
+  </si>
+  <si>
+    <t>2706</t>
+  </si>
+  <si>
+    <t>2180</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>2.11%</t>
+  </si>
+  <si>
+    <t>602725760737183</t>
+  </si>
+  <si>
+    <t>Lámpara LED blanca TIANLAI de 6500K, con luz suave, con conector en rosca E27 estándar, es fácil de instalar, tiene una potencia de 12 vatios, es energéticamente eficiente y tiene una hermética sellación, tiene una larga duración útil. Es adecuada para la iluminación interior y se puede utilizar en hogares y oficinas.</t>
+  </si>
+  <si>
+    <t>1443</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>3.26%</t>
+  </si>
+  <si>
+    <t>605007529264104</t>
+  </si>
+  <si>
+    <t>1 Pza, Lámpara Tipo Minero，Lámpare Portátil，Linterna De Cabeza De Emergencia Con 8 Modos De Iluminación, 3 Leds, Doble Interruptor Para La Luz Principal Y Secundaria, Una Batería Recargable De 1800 Mah Con Conector Type - C. Es Duradera Y Adecuada Para Senderismo, Camping, Carrera, Pesca, Caza, Reparaciones De Emergencia Y Otros Escenarios.</t>
+  </si>
+  <si>
+    <t>2522</t>
+  </si>
+  <si>
+    <t>2156</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>2.85%</t>
+  </si>
+  <si>
+    <t>602675966000184</t>
+  </si>
+  <si>
+    <t>Linkbits, Altavoz Portátil Inalámbrico,Parlantes BT portátiles， Inalámbricos Altavoz Bluetooth, Altavoz Estéreo Para Música, Con Diseño De Aluminio, Sonido Claro, Interfaces USB Y AUX, Función De Radio FM, Es Una Excelente Compañía Para Relajarse En Casa O En Fiestas Al Aire Libre</t>
+  </si>
+  <si>
+    <t>2811</t>
+  </si>
+  <si>
+    <t>2233</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>1.78%</t>
+  </si>
+  <si>
+    <t>603000705778049</t>
+  </si>
+  <si>
+    <t>Auriculares Inalámbricos con Ganchos en Forma de Gato, Luces LED Coloridas, Batería Recargable (8h de Música), Compatible con TF/FM/AUX - Ideal para Juegos, Estudio, Trabajo y Viajes</t>
+  </si>
+  <si>
+    <t>813</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2.83%</t>
+  </si>
+  <si>
+    <t>602755825509188</t>
+  </si>
+  <si>
+    <t>MEGALUZ Luminario LED Empotrable, 18W, 1260lm, Luz Fría 6500K, Foco de Techo de 175mm Brillante y Eficiente Energéticamente</t>
+  </si>
+  <si>
+    <t>1949</t>
+  </si>
+  <si>
+    <t>1539</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>3.59%</t>
+  </si>
+  <si>
+    <t>602310021320192</t>
+  </si>
+  <si>
+    <t>Auriculares Inalámbricos de Cabeza, Recargables con Luces Coloridas y Adorables Formas de Orejas de Gato，Gran Capacidad de Batería para 7 Horas de Reproducción Musical，Telescópicos y Doblables, Fáciles de Llevar，Compatible con Teléfonos, Computadoras y Tablets. Ideal para Música, Juegos, Estudio en línea y Trabajo. El Regalo Ideal para Amigo</t>
   </si>
   <si>
     <t>869</t>
   </si>
   <si>
+    <t>707</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>3.34%</t>
+  </si>
+  <si>
+    <t>602749181752981</t>
+  </si>
+  <si>
+    <t>Audífonos BT Inalámbricos 50h Batería - Diseño Ajustable y Ultra Cómodo, Compatible con Tablet/PC/TV/Celular, Regalo Perfecto para Viajes (Estilo Macaron)</t>
+  </si>
+  <si>
+    <t>2133</t>
+  </si>
+  <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>2.20%</t>
+  </si>
+  <si>
+    <t>603046339823835</t>
+  </si>
+  <si>
+    <t>Tira de Luces LED 5M Súper Brillante - Cortable a Medida, 120 diodos LEDs de Alta Luminosidad, 50,000 Horas de Duración, ¡Ideal para Decoración Interior y Exterior</t>
+  </si>
+  <si>
+    <t>3592</t>
+  </si>
+  <si>
+    <t>2866</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>602234054143574</t>
+  </si>
+  <si>
+    <t>Emparejamiento estéreo inalámbrico portátil con luz RGB, luz de ritmo multicolor, tarjeta TF USB, radio FM, emparejamiento doble,2-4 horas de tiempo de reproducción para viajar/fiesta/cine en casa/al aire libre</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>602573893430755</t>
+  </si>
+  <si>
+    <t>5 m/16.4ft Tira de luces LED con RGB, control remoto, Cortar longitud como desee, conexión USB, 12 colores libremente intercambiables, 4 modos de parpadeo de luz, luz de ambiente creativa, decoración con retroiluminación de tv a color para ambientes de salón y dormitorio</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>602596978823873</t>
+  </si>
+  <si>
+    <t>Altavoz Inalámbrico Portátil Anticaída para Exteriores, Conecta Inalámbricamente a Celulares y Computadoras, con Super Bajos Potentes y Luces LED. Compatible con Tarjeta TF, USB, Radio FM y Conexión Inalámbrica. Con Micrófono Integrado para Karaoke. Ideal para Presentaciones Musicales en Vivo y Fiestas en Casa.</t>
+  </si>
+  <si>
+    <t>563</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2.66%</t>
+  </si>
+  <si>
+    <t>602672140792857</t>
+  </si>
+  <si>
+    <t>Soporte TV Pared 26-60" - Material Reforzado, Fácil Montaje, Ahorra Espacio Garantizado</t>
+  </si>
+  <si>
+    <t>981</t>
+  </si>
+  <si>
+    <t>804</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>3.67%</t>
+  </si>
+  <si>
+    <t>602717237949231</t>
+  </si>
+  <si>
+    <t>Bebedero infantil de diseño cartoon, taza de aprendizaje para niños, utensilio de cocina de experiencia, en forma de adorable rana, incluye 2 vasos, fácil de usar, regalo ideal para niños en festividades</t>
+  </si>
+  <si>
+    <t>602736833704793</t>
+  </si>
+  <si>
+    <t>¡EDICIÓN LIMITADA! Bocina Turbo Bass con Luz Party RGB - 12 Horas de Música + Carga Rápida, Sonido 360° para Playa y Camping - Certificada por Ingenieros Mexicanos (Regalo San Valentín con Mix de Amor en Españo）</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>602761865323826</t>
+  </si>
+  <si>
+    <t>Linkbits ，Bocina Portátil，Parlantes BT portátiles，Ideal Para Fiestas Y Aventuras Al Aire Libre，Modelo Compacto Altavoz， Con Soporte Para Teléfono Móvil, Asa De Transporte, Función De Radio FM, Luces De Ambiente Y Batería Recargable</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>40.00%</t>
+  </si>
+  <si>
+    <t>602852596545121</t>
+  </si>
+  <si>
+    <t>Linkbits，Bocina Portátil ，Parlantes Bt Portátiles，Con Iluminación De Ambiente Incorporada. Tiene Una Duración De 1 Hora Y Cuenta Con Radio Fm, Función Tws (True Wireless Stereo), Y Soporta Tarjetas Tf Y Micro Sd. Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
+  </si>
+  <si>
+    <t>685</t>
+  </si>
+  <si>
+    <t>576</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1.31%</t>
+  </si>
+  <si>
+    <t>603059761601319</t>
+  </si>
+  <si>
+    <t>Altavoz Inalámbrico Portátil con Diseño Retro, Bajos Optimizados y Sonido 3D Envolvente,Compatible con TF/FM/AUX, Conexión BT TWS. Ideal para Home Theater, Fiestas y Regalos​</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>794</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>1.79%</t>
+  </si>
+  <si>
+    <t>603149955891617</t>
+  </si>
+  <si>
+    <t>Audífonos inalámbricos plegables con luces LED, graves profundos y 8h de duración. Compatibles con cable de 3.5mm, carga MicroUSB, FM y controles de volumen. Ideales para viajes, estudio, juegos y trabajo. ¡Ligeros y versátiles</t>
+  </si>
+  <si>
+    <t>603204649611449</t>
+  </si>
+  <si>
+    <t>Bombilla LED de bulbo esférico de 9 W con conector E27 de TIANLAI, bombilla RGB que puede cambiar de color a través del control remoto, con 16 opciones de color, multicolor y ajustable. Tiene un voltaje de funcionamiento de 85-265 V y una frecuencia de 60 Hz, y es adecuada para fiestas, habitaciones y el hogar</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>603241827944670</t>
+  </si>
+  <si>
+    <t>TIANLAI，Ventilador De Techo LED，Enchufe E2，De 32 Vatios, De 11 Pulgadas, Con Control Remoto, Tonalidad De Luz Ajustable, Tres Modos. Con Un Flujo Luminoso De 2000 Lm,Adecuado Para Habitaciones Infantiles, Estudios Y Comedores De Estilo Moderno</t>
+  </si>
+  <si>
+    <t>604435224858554</t>
+  </si>
+  <si>
+    <t>Linkbits Bocina Portátil De Bt, Tiene Luces De Ambiente Incorporadas. La Duración De La Batería Es De 2 Horas. Soporta La Radio Fm, Posee La Función Tws (True Wireless Stereo), Admite Tarjetas Tf Y Se Puede Cargar A Través De Usb. Con Solo 180G, Es Compacta Y Liviana. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
+  </si>
+  <si>
+    <t>604456699682907</t>
+  </si>
+  <si>
+    <t>Altavoz BT Inalámbrico KBroad, Bocina Portátil de Madera con Soporte para Móvil, Hi-Fi Calidad de Sonido, 2 Altavoces de 12W de Alta Resolución, Batería Recargable 1200mAh (2-3h de reproducción), FM, TWS y Carga TYPE-C. Ideal para Cine Doméstico, Fiestas y Eventos al Aire Libre.</t>
+  </si>
+  <si>
+    <t>604733775430734</t>
+  </si>
+  <si>
+    <t>LINKBITS Auriculares TWS Bluetooth 5.3 Inalámbricos - Semiintraurales 45° con Cancelación de Ruido 6 Mic, Autonomía 24h, Sonido Hi-Fi 13mm y Control por Toque Inteligente para Deportes, Trabajo y Viajes</t>
+  </si>
+  <si>
+    <t>3063</t>
+  </si>
+  <si>
+    <t>2441</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>2.84%</t>
+  </si>
+  <si>
+    <t>604791489028353</t>
+  </si>
+  <si>
+    <t>Enfriador de Aire Evaporativo Portátil 6 Pulgadas | Ideal para Hogar Oficina Escritorio Viaje, 280ml Depósito de Agua, 3 Velocidades de Viento, Rociador 3 Agujeros, Rotación 270°</t>
+  </si>
+  <si>
+    <t>5.88%</t>
+  </si>
+  <si>
+    <t>604830361841963</t>
+  </si>
+  <si>
+    <t>1PZA, Lámpara de Emergencia, Lámpara Portátil con Pinza y Cordel Elástico. Es la Mejor Linterna para Corredores, también Ideal como Faro para Bicicletas. Sirve como Luz de Seguridad para Aquellos que Caminan por la Noche o Caminan con Sus Perros, y también como Linterna de Trabajo de Emergencia. Mejora la Visibilidad y es un Equipamiento Esencial para la Seguridad Nocturna</t>
+  </si>
+  <si>
+    <t>632</t>
+  </si>
+  <si>
+    <t>539</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>3.32%</t>
+  </si>
+  <si>
+    <t>605219375164979</t>
+  </si>
+  <si>
+    <t>Bocina Portátil Bluetooth 5.3, Radio FM y Reproductor USB, Ventilador Integrado Recargable, Sonido de Calidad, Carga Tipo-C, para Hogar, Oficina, Dormitorio y Salidas</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1.09%</t>
+  </si>
+  <si>
+    <t>605306079814264</t>
+  </si>
+  <si>
+    <t>Mascarillas Infantiles KF94 10 pcs, Cuatro Capas de Protección con Tejido de Fusión Filtrante, Patrones Divertidos, Piel Amigable y Transpirable</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>1.91%</t>
+  </si>
+  <si>
+    <t>605381191425380</t>
+  </si>
+  <si>
+    <t>1 Pza, Lámpara Tipo Minero，Lámpare Portátil，Linterna De Cabeza De Emergencia Con 8 Modos De Iluminación, 64Leds, Doble Interruptor Para La Luz Principal Y Secundaria, Una Batería Recargable De 1800 Mah Con Conector Type - C. Es Duradera Y Adecuada Para Senderismo, Camping, Carrera, Pesca, Caza, Reparaciones De Emergencia Y Otros Escenarios.</t>
+  </si>
+  <si>
+    <t>605398153150879</t>
+  </si>
+  <si>
+    <t>MEGALUZ Lámpara Solar para Exterior 2250LM 7000K con Botón de Encendido, Sensor de Movimiento 5m, IP65, Brazo Ajustable, Sin Cables, Luz LED para Hogar, Patio, Calle y Cochera</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
     <t>728</t>
   </si>
   <si>
-    <t>1.35%</t>
-  </si>
-  <si>
-    <t>602366728346713</t>
-  </si>
-  <si>
-    <t>Megaluz，Ventilador de Techo con Lámpara LED，de 13 Pulgadas， 4 Velocidades, 6 Aspas, Control Remoto, 24 vatios Regulables, Flujo Luminoso de 2200 lm, Silencioso y Eficiente,Adecuado para Dormitorios y Salas</t>
-  </si>
-  <si>
-    <t>24856</t>
-  </si>
-  <si>
-    <t>19751</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t>1.69%</t>
-  </si>
-  <si>
-    <t>602378203945399</t>
-  </si>
-  <si>
-    <t>Dispensador de Agua para Garrafón 5L a 20L, Bomba Eléctrica Recargable USB, Flujo rápido 1500ml/min, tubo de salida acero inoxidable 304, portátil y compacto, cuerpo duradero ABS+PP, fácil instalación y operación con un solo botón, ideal para hogar, cocina, oficina y camping, práctico para uso diario en casa y exteriores.</t>
-  </si>
-  <si>
-    <t>33605</t>
-  </si>
-  <si>
-    <t>28117</t>
-  </si>
-  <si>
-    <t>522</t>
-  </si>
-  <si>
-    <t>441</t>
-  </si>
-  <si>
-    <t>1.55%</t>
-  </si>
-  <si>
-    <t>604800615833335</t>
-  </si>
-  <si>
-    <t>Cable Extensión Eléctrico Blanco SPT-2 18 AWG 2 Hilos, PVC Retardante al Fuego con Enchufe Plano Polarizado, Cable Eléctrico Seguro para Uso Interior en Casa y Oficina</t>
-  </si>
-  <si>
-    <t>4256</t>
-  </si>
-  <si>
-    <t>3366</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>1.83%</t>
-  </si>
-  <si>
-    <t>604950620924263</t>
-  </si>
-  <si>
-    <t>Abanico portátil, ventilador evaporativo de enfriamiento con pulverización y luz nocturna, 3 velocidades ajustables, funcionamiento silencioso, alimentación USB TYPE-C, compacto con asa, abanico multifuncional para el hogar y escritorio.</t>
-  </si>
-  <si>
-    <t>8883</t>
-  </si>
-  <si>
-    <t>6429</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>2.53%</t>
-  </si>
-  <si>
-    <t>604735604161733</t>
-  </si>
-  <si>
-    <t>La bocina portátil inalámbrica Linkbits cuenta con parlantes estéreo de dos altavoces de 3 pulgadas, luces de ambiente integradas y una batería recargable de gran capacidad que ofrece 3-4 horas de reproducción. Compatible con tarjeta TF, USB, radio FM y conexión inalámbrica, es ideal para cine en casa, fiestas al aire libre y campamentos.</t>
-  </si>
-  <si>
-    <t>22176</t>
-  </si>
-  <si>
-    <t>18412</t>
-  </si>
-  <si>
-    <t>555</t>
-  </si>
-  <si>
-    <t>489</t>
-  </si>
-  <si>
-    <t>2.50%</t>
-  </si>
-  <si>
-    <t>604556557710403</t>
-  </si>
-  <si>
-    <t>KBroad Altavoz BT, con 1 Micrófono Inalámbrico Gratis, Altavoz para Karaoke con Calidad HiFi, 2 Altavoces de 6W de Buena Calidad, Modo Luz RGB, Batería de Carga Integrada de 1800mAh (2-3 Horas de Duración), Compatibilidad con Tarjeta TF, Radio FM y Función TWS, Carga por TYPE-C. Ideal para Home Cinema, Karaoke y Actividades al Aire Libre.</t>
-  </si>
-  <si>
-    <t>14139</t>
-  </si>
-  <si>
-    <t>11093</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>1.80%</t>
-  </si>
-  <si>
-    <t>605011069265793</t>
-  </si>
-  <si>
-    <t>Auriculares Bluetooth 5.3 supraaurales plegables y ligeros, adecuados para todas las edades, con almohadillas transpirables, controlador de grafeno y 3 modos de conexión: Bluetooth, tarjeta TF y cableado</t>
-  </si>
-  <si>
-    <t>12134</t>
-  </si>
-  <si>
-    <t>9711</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>1.90%</t>
-  </si>
-  <si>
-    <t>604903426610284</t>
-  </si>
-  <si>
-    <t>MEGALUZ Foco LED de 20W-60W, 1800-5700 lm Ultra brillante, luz blanca fría de 6500K, base E27, ahorro energético y alta eficiencia para hogar, tienda y garaje</t>
-  </si>
-  <si>
-    <t>1645</t>
-  </si>
-  <si>
-    <t>1306</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>3.89%</t>
-  </si>
-  <si>
-    <t>604925924855305</t>
-  </si>
-  <si>
-    <t>MEGALUZ Tomacorrientes de Pared USB con 2 Puertos USB y 2 Tomacorrientes Estándar: Carga Rápida, Instalación Fácil, Resistencia a Altas Temperaturas y Materiales de Alta Calidad y Alto Rendimiento</t>
-  </si>
-  <si>
-    <t>1819</t>
-  </si>
-  <si>
-    <t>1488</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>2.14%</t>
-  </si>
-  <si>
-    <t>602725760737183</t>
-  </si>
-  <si>
-    <t>Lámpara LED blanca TIANLAI de 6500K, con luz suave, con conector en rosca E27 estándar, es fácil de instalar, tiene una potencia de 12 vatios, es energéticamente eficiente y tiene una hermética sellación, tiene una larga duración útil. Es adecuada para la iluminación interior y se puede utilizar en hogares y oficinas.</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>934</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>3.51%</t>
-  </si>
-  <si>
-    <t>604860426636252</t>
-  </si>
-  <si>
-    <t>【TIANLAI】Cabeza de farola, 100W, múltiples ledes 2835/5000lm, vida útil larga de 50000h, amplio rango de iluminación, buena impermeabilidad y disipación de calor, se instala con varios estilos de postes, voltaje de trabajo 127V, ideal para canchas de deporte, carreteras, túneles y otros escenarios.</t>
-  </si>
-  <si>
-    <t>1286</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2.80%</t>
-  </si>
-  <si>
-    <t>602675966000184</t>
-  </si>
-  <si>
-    <t>Linkbits, Altavoz Portátil Inalámbrico,Parlantes BT portátiles， Inalámbricos Altavoz Bluetooth, Altavoz Estéreo Para Música, Con Diseño De Aluminio, Sonido Claro, Interfaces USB Y AUX, Función De Radio FM, Es Una Excelente Compañía Para Relajarse En Casa O En Fiestas Al Aire Libre</t>
-  </si>
-  <si>
-    <t>1932</t>
-  </si>
-  <si>
-    <t>1541</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>16</t>
   </si>
   <si>
     <t>1.92%</t>
   </si>
   <si>
-    <t>602936750997572</t>
-  </si>
-  <si>
-    <t>¡Apto para múltiples escenarios! La lámpara LED de hojas de la marca TIANLAI, con una potencia de 36 vatios, tiene un conector E27 universal y un panel plegable de 4 hojas. El blanco brillante de 6500K es adecuado tanto para salones, dormitorios, cocinas como para garajes.</t>
-  </si>
-  <si>
-    <t>2692</t>
-  </si>
-  <si>
-    <t>2235</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>1.82%</t>
-  </si>
-  <si>
-    <t>602310021320192</t>
-  </si>
-  <si>
-    <t>Auriculares Inalámbricos de Cabeza, Recargables con Luces Coloridas y Adorables Formas de Orejas de Gato，Gran Capacidad de Batería para 7 Horas de Reproducción Musical，Telescópicos y Doblables, Fáciles de Llevar，Compatible con Teléfonos, Computadoras y Tablets. Ideal para Música, Juegos, Estudio en línea y Trabajo. El Regalo Ideal para Amigo</t>
-  </si>
-  <si>
-    <t>589</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>2.72%</t>
-  </si>
-  <si>
-    <t>603046339823835</t>
-  </si>
-  <si>
-    <t>Tira de Luces LED 5M Súper Brillante - Cortable a Medida, 120 diodos LEDs de Alta Luminosidad, 50,000 Horas de Duración, ¡Ideal para Decoración Interior y Exterior</t>
-  </si>
-  <si>
-    <t>2337</t>
-  </si>
-  <si>
-    <t>1869</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>1.67%</t>
-  </si>
-  <si>
-    <t>605007529264104</t>
-  </si>
-  <si>
-    <t>1 Pza, Lámpara Tipo Minero，Lámpare Portátil，Linterna De Cabeza De Emergencia Con 8 Modos De Iluminación, 3 Leds, Doble Interruptor Para La Luz Principal Y Secundaria, Una Batería Recargable De 1800 Mah Con Conector Type - C. Es Duradera Y Adecuada Para Senderismo, Camping, Carrera, Pesca, Caza, Reparaciones De Emergencia Y Otros Escenarios.</t>
-  </si>
-  <si>
-    <t>1558</t>
-  </si>
-  <si>
-    <t>1350</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>2.57%</t>
-  </si>
-  <si>
-    <t>602234054143574</t>
-  </si>
-  <si>
-    <t>Emparejamiento estéreo inalámbrico portátil con luz RGB, luz de ritmo multicolor, tarjeta TF USB, radio FM, emparejamiento doble,2-4 horas de tiempo de reproducción para viajar/fiesta/cine en casa/al aire libre</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>602573893430755</t>
-  </si>
-  <si>
-    <t>5 m/16.4ft Tira de luces LED con RGB, control remoto, Cortar longitud como desee, conexión USB, 12 colores libremente intercambiables, 4 modos de parpadeo de luz, luz de ambiente creativa, decoración con retroiluminación de tv a color para ambientes de salón y dormitorio</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>602596978823873</t>
-  </si>
-  <si>
-    <t>Altavoz Inalámbrico Portátil Anticaída para Exteriores, Conecta Inalámbricamente a Celulares y Computadoras, con Super Bajos Potentes y Luces LED. Compatible con Tarjeta TF, USB, Radio FM y Conexión Inalámbrica. Con Micrófono Integrado para Karaoke. Ideal para Presentaciones Musicales en Vivo y Fiestas en Casa.</t>
-  </si>
-  <si>
-    <t>387</t>
-  </si>
-  <si>
-    <t>335</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>3.88%</t>
-  </si>
-  <si>
-    <t>602672140792857</t>
-  </si>
-  <si>
-    <t>Soporte TV Pared 26-60" - Material Reforzado, Fácil Montaje, Ahorra Espacio Garantizado</t>
-  </si>
-  <si>
-    <t>702</t>
-  </si>
-  <si>
-    <t>563</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>3.99%</t>
-  </si>
-  <si>
-    <t>602736833704793</t>
-  </si>
-  <si>
-    <t>¡EDICIÓN LIMITADA! Bocina Turbo Bass con Luz Party RGB - 12 Horas de Música + Carga Rápida, Sonido 360° para Playa y Camping - Certificada por Ingenieros Mexicanos (Regalo San Valentín con Mix de Amor en Españo）</t>
-  </si>
-  <si>
-    <t>602749181752981</t>
-  </si>
-  <si>
-    <t>Audífonos BT Inalámbricos 50h Batería - Diseño Ajustable y Ultra Cómodo, Compatible con Tablet/PC/TV/Celular, Regalo Perfecto para Viajes (Estilo Macaron)</t>
-  </si>
-  <si>
-    <t>1419</t>
-  </si>
-  <si>
-    <t>1092</t>
-  </si>
-  <si>
-    <t>2.54%</t>
-  </si>
-  <si>
-    <t>602755825509188</t>
-  </si>
-  <si>
-    <t>MEGALUZ Luminario LED Empotrable, 18W, 1260lm, Luz Fría 6500K, Foco de Techo de 175mm Brillante y Eficiente Energéticamente</t>
-  </si>
-  <si>
-    <t>1316</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>3.27%</t>
-  </si>
-  <si>
-    <t>602761865323826</t>
-  </si>
-  <si>
-    <t>Linkbits ，Bocina Portátil，Parlantes BT portátiles，Ideal Para Fiestas Y Aventuras Al Aire Libre，Modelo Compacto Altavoz， Con Soporte Para Teléfono Móvil, Asa De Transporte, Función De Radio FM, Luces De Ambiente Y Batería Recargable</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>66.67%</t>
-  </si>
-  <si>
-    <t>602852596545121</t>
-  </si>
-  <si>
-    <t>Linkbits，Bocina Portátil ，Parlantes Bt Portátiles，Con Iluminación De Ambiente Incorporada. Tiene Una Duración De 1 Hora Y Cuenta Con Radio Fm, Función Tws (True Wireless Stereo), Y Soporta Tarjetas Tf Y Micro Sd. Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
-  </si>
-  <si>
-    <t>474</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1.27%</t>
-  </si>
-  <si>
-    <t>603000705778049</t>
-  </si>
-  <si>
-    <t>Auriculares Inalámbricos con Ganchos en Forma de Gato, Luces LED Coloridas, Batería Recargable (8h de Música), Compatible con TF/FM/AUX - Ideal para Juegos, Estudio, Trabajo y Viajes</t>
-  </si>
-  <si>
-    <t>539</t>
-  </si>
-  <si>
-    <t>435</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>603059761601319</t>
-  </si>
-  <si>
-    <t>Altavoz Inalámbrico Portátil con Diseño Retro, Bajos Optimizados y Sonido 3D Envolvente,Compatible con TF/FM/AUX, Conexión BT TWS. Ideal para Home Theater, Fiestas y Regalos​</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>1.77%</t>
-  </si>
-  <si>
-    <t>603204649611449</t>
-  </si>
-  <si>
-    <t>Bombilla LED de bulbo esférico de 9 W con conector E27 de TIANLAI, bombilla RGB que puede cambiar de color a través del control remoto, con 16 opciones de color, multicolor y ajustable. Tiene un voltaje de funcionamiento de 85-265 V y una frecuencia de 60 Hz, y es adecuada para fiestas, habitaciones y el hogar</t>
-  </si>
-  <si>
-    <t>603241827944670</t>
-  </si>
-  <si>
-    <t>TIANLAI，Ventilador De Techo LED，Enchufe E2，De 32 Vatios, De 11 Pulgadas, Con Control Remoto, Tonalidad De Luz Ajustable, Tres Modos. Con Un Flujo Luminoso De 2000 Lm,Adecuado Para Habitaciones Infantiles, Estudios Y Comedores De Estilo Moderno</t>
-  </si>
-  <si>
-    <t>604435224858554</t>
-  </si>
-  <si>
-    <t>Linkbits Bocina Portátil De Bt, Tiene Luces De Ambiente Incorporadas. La Duración De La Batería Es De 2 Horas. Soporta La Radio Fm, Posee La Función Tws (True Wireless Stereo), Admite Tarjetas Tf Y Se Puede Cargar A Través De Usb. Con Solo 180G, Es Compacta Y Liviana. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
-  </si>
-  <si>
-    <t>604456699682907</t>
-  </si>
-  <si>
-    <t>Altavoz BT Inalámbrico KBroad, Bocina Portátil de Madera con Soporte para Móvil, Hi-Fi Calidad de Sonido, 2 Altavoces de 12W de Alta Resolución, Batería Recargable 1200mAh (2-3h de reproducción), FM, TWS y Carga TYPE-C. Ideal para Cine Doméstico, Fiestas y Eventos al Aire Libre.</t>
-  </si>
-  <si>
-    <t>604733775430734</t>
-  </si>
-  <si>
-    <t>LINKBITS Auriculares TWS Bluetooth 5.3 Inalámbricos - Semiintraurales 45° con Cancelación de Ruido 6 Mic, Autonomía 24h, Sonido Hi-Fi 13mm y Control por Toque Inteligente para Deportes, Trabajo y Viajes</t>
-  </si>
-  <si>
-    <t>2052</t>
-  </si>
-  <si>
-    <t>1650</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>3.07%</t>
-  </si>
-  <si>
-    <t>604791489028353</t>
-  </si>
-  <si>
-    <t>Enfriador de Aire Evaporativo Portátil 6 Pulgadas | Ideal para Hogar Oficina Escritorio Viaje, 280ml Depósito de Agua, 3 Velocidades de Viento, Rociador 3 Agujeros, Rotación 270°</t>
-  </si>
-  <si>
-    <t>2.56%</t>
-  </si>
-  <si>
-    <t>604830361841963</t>
-  </si>
-  <si>
-    <t>1PZA, Lámpara de Emergencia, Lámpara Portátil con Pinza y Cordel Elástico. Es la Mejor Linterna para Corredores, también Ideal como Faro para Bicicletas. Sirve como Luz de Seguridad para Aquellos que Caminan por la Noche o Caminan con Sus Perros, y también como Linterna de Trabajo de Emergencia. Mejora la Visibilidad y es un Equipamiento Esencial para la Seguridad Nocturna</t>
-  </si>
-  <si>
-    <t>432</t>
-  </si>
-  <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>3.70%</t>
-  </si>
-  <si>
-    <t>605219375164979</t>
-  </si>
-  <si>
-    <t>Bocina Portátil Bluetooth 5.3, Radio FM y Reproductor USB, Ventilador Integrado Recargable, Sonido de Calidad, Carga Tipo-C, para Hogar, Oficina, Dormitorio y Salidas</t>
-  </si>
-  <si>
-    <t>787</t>
-  </si>
-  <si>
-    <t>662</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>605306079814264</t>
-  </si>
-  <si>
-    <t>Mascarillas Infantiles KF94 10 pcs, Cuatro Capas de Protección con Tejido de Fusión Filtrante, Patrones Divertidos, Piel Amigable y Transpirable</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>1.41%</t>
-  </si>
-  <si>
-    <t>605381191425380</t>
-  </si>
-  <si>
-    <t>1 Pza, Lámpara Tipo Minero，Lámpare Portátil，Linterna De Cabeza De Emergencia Con 8 Modos De Iluminación, 64Leds, Doble Interruptor Para La Luz Principal Y Secundaria, Una Batería Recargable De 1800 Mah Con Conector Type - C. Es Duradera Y Adecuada Para Senderismo, Camping, Carrera, Pesca, Caza, Reparaciones De Emergencia Y Otros Escenarios.</t>
-  </si>
-  <si>
-    <t>605398153150879</t>
-  </si>
-  <si>
-    <t>MEGALUZ Lámpara Solar para Exterior 2250LM 7000K con Botón de Encendido, Sensor de Movimiento 5m, IP65, Brazo Ajustable, Sin Cables, Luz LED para Hogar, Patio, Calle y Cochera</t>
-  </si>
-  <si>
-    <t>530</t>
-  </si>
-  <si>
-    <t>466</t>
-  </si>
-  <si>
-    <t>1.89%</t>
-  </si>
-  <si>
-    <t>605444542175386</t>
-  </si>
-  <si>
-    <t>Linkbits Bocina Portátil BT Está Equipada Con Un Altavoz De 8 Pulgadas Y Luces De Ambiente Incorporadas. Tiene Una Duración De 2 Horas Y Viene Con Un Micrófono Cableado. Es Compatible Con La Radio FM Y La Función TWS (True Wireless Stereo), Soporta Tarjetas TF Y Se Puede Conectar A Través De USB. Cuenta Con Una Asa Y Una Pantalla De Visualización, Y También Tiene La Función De Ajuste De EQ Para El Sonido. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
-  </si>
-  <si>
-    <t>3696</t>
-  </si>
-  <si>
-    <t>2715</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>2.98%</t>
+    <t>605431657287236</t>
+  </si>
+  <si>
+    <t>TrendBox - foco LED E27 de 3 W giratoria a todo color, con bola de vidrio automática, 85-265 V, mini lámpara de fiesta, ahorro de energía, disco DJ</t>
   </si>
 </sst>
 </file>
@@ -748,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1073,10 +1121,10 @@
         <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -1084,25 +1132,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -1110,25 +1158,25 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1136,25 +1184,25 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
@@ -1162,25 +1210,25 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
@@ -1188,25 +1236,25 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
@@ -1214,25 +1262,25 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
@@ -1240,25 +1288,25 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20">
@@ -1266,25 +1314,25 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F20" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21">
@@ -1292,25 +1340,25 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22">
@@ -1318,25 +1366,25 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F22" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G22" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H22" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -1344,25 +1392,25 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="F23" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G23" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="H23" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
@@ -1370,25 +1418,25 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="H24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25">
@@ -1396,25 +1444,25 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F25" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G25" t="s">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="H25" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26">
@@ -1422,25 +1470,25 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E26" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G26" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="H26" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27">
@@ -1448,25 +1496,25 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="F27" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="G27" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="H27" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28">
@@ -1474,25 +1522,25 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E28" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G28" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="H28" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -1500,25 +1548,25 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C29" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" t="s">
         <v>169</v>
       </c>
-      <c r="D29" t="s">
-        <v>170</v>
-      </c>
-      <c r="E29" t="s">
-        <v>171</v>
-      </c>
-      <c r="F29" t="s">
-        <v>130</v>
-      </c>
       <c r="G29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30">
@@ -1526,25 +1574,25 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="F30" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="G30" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="H30" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -1552,25 +1600,25 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="F31" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="G31" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H31" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32">
@@ -1578,25 +1626,25 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="F32" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="H32" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33">
@@ -1604,25 +1652,25 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="F33" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="G33" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="H33" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34">
@@ -1630,25 +1678,25 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="H34" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35">
@@ -1656,25 +1704,25 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C35" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="F35" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="G35" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="H35" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36">
@@ -1682,25 +1730,25 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C36" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D36" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="G36" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="H36" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37">
@@ -1708,25 +1756,25 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C37" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D37" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E37" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F37" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G37" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="H37" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38">
@@ -1734,25 +1782,25 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C38" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>202</v>
+        <v>62</v>
       </c>
       <c r="E38" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="G38" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="H38" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39">
@@ -1760,25 +1808,25 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="F39" t="s">
-        <v>120</v>
+        <v>212</v>
       </c>
       <c r="G39" t="s">
-        <v>120</v>
+        <v>212</v>
       </c>
       <c r="H39" t="s">
-        <v>121</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40">
@@ -1786,25 +1834,25 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C40" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F40" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="G40" t="s">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="H40" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41">
@@ -1812,25 +1860,103 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C41" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D41" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F41" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="G41" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="H41" t="s">
-        <v>218</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C42" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>227</v>
+      </c>
+      <c r="C43" t="s">
+        <v>228</v>
+      </c>
+      <c r="D43" t="s">
+        <v>229</v>
+      </c>
+      <c r="E43" t="s">
+        <v>230</v>
+      </c>
+      <c r="F43" t="s">
+        <v>231</v>
+      </c>
+      <c r="G43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>233</v>
+      </c>
+      <c r="C44" t="s">
+        <v>234</v>
+      </c>
+      <c r="D44" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" t="s">
+        <v>151</v>
+      </c>
+      <c r="F44" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
